--- a/Resources/Languages/Languages.xlsx
+++ b/Resources/Languages/Languages.xlsx
@@ -1,64 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet name="en" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="en" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={3E6082AE-427E-4561-BB04-4FFC2BCC68EC}</author>
+    <author>tc={9299A9CA-65C3-488D-A61A-5D15F38B91BC}</author>
+    <author>tc={3A800AE9-6966-4314-9858-99499E309450}</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" xr:uid="{3E6082AE-427E-4561-BB04-4FFC2BCC68EC}">
       <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Settings menu</t>
+          <t xml:space="preserve">Unknown Author:</t>
         </r>
-      </text>
-    </comment>
-    <comment ref="D30" authorId="0">
-      <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Store content
+          <t xml:space="preserve">
+Settings menu
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="D50" authorId="0">
+    <comment ref="D30" authorId="1" xr:uid="{9299A9CA-65C3-488D-A61A-5D15F38B91BC}">
       <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Disclaimer content</t>
+          <t xml:space="preserve">Unknown Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Store content
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D50" authorId="2" xr:uid="{3A800AE9-6966-4314-9858-99499E309450}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Unknown Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Disclaimer content
+</t>
         </r>
       </text>
     </comment>
@@ -69,61 +94,61 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
-    <t xml:space="preserve">key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">store_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Магазин</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settings_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Настройки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settings_graphics_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graphics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Графика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settings_audio_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Звук</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settings_game_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Игра</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coin_particles_amount</t>
+    <t>key</t>
+  </si>
+  <si>
+    <t>En</t>
+  </si>
+  <si>
+    <t>Ru</t>
+  </si>
+  <si>
+    <t>store_btn</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Магазин</t>
+  </si>
+  <si>
+    <t>settings_btn</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Настройки</t>
+  </si>
+  <si>
+    <t>settings_graphics_btn</t>
+  </si>
+  <si>
+    <t>Graphics</t>
+  </si>
+  <si>
+    <t>Графика</t>
+  </si>
+  <si>
+    <t>settings_audio_btn</t>
+  </si>
+  <si>
+    <t>Audio</t>
+  </si>
+  <si>
+    <t>Звук</t>
+  </si>
+  <si>
+    <t>settings_game_btn</t>
+  </si>
+  <si>
+    <t>Game</t>
+  </si>
+  <si>
+    <t>Игра</t>
+  </si>
+  <si>
+    <t>coin_particles_amount</t>
   </si>
   <si>
     <t xml:space="preserve">Coin particles</t>
@@ -132,34 +157,34 @@
     <t xml:space="preserve">Кол. частиц монет</t>
   </si>
   <si>
-    <t xml:space="preserve">coin_amount_dropdown_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Много</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coin_amount_dropdown_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Середина</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coin_amount_dropdown_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мало</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coin_amount_dropdown_4</t>
+    <t>coin_amount_dropdown_1</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Много</t>
+  </si>
+  <si>
+    <t>coin_amount_dropdown_2</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Середина</t>
+  </si>
+  <si>
+    <t>coin_amount_dropdown_3</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Мало</t>
+  </si>
+  <si>
+    <t>coin_amount_dropdown_4</t>
   </si>
   <si>
     <t xml:space="preserve">Very Low</t>
@@ -168,16 +193,16 @@
     <t xml:space="preserve">Очень мало</t>
   </si>
   <si>
-    <t xml:space="preserve">coin_amount_dropdown_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отключено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coin_particles_amount_description</t>
+    <t>coin_amount_dropdown_5</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>Отключено</t>
+  </si>
+  <si>
+    <t>coin_particles_amount_description</t>
   </si>
   <si>
     <t xml:space="preserve">Changes the amount of coins on screen,\n can improve performance on low-end devices.</t>
@@ -186,7 +211,7 @@
     <t xml:space="preserve">Меняет количество монет на екране, может увеличить\nпроизводительность на слабых устройствах.</t>
   </si>
   <si>
-    <t xml:space="preserve">enemy_animations</t>
+    <t>enemy_animations</t>
   </si>
   <si>
     <t xml:space="preserve">Enemy animations</t>
@@ -195,7 +220,7 @@
     <t xml:space="preserve">Анимация противника</t>
   </si>
   <si>
-    <t xml:space="preserve">enemy_animations_description</t>
+    <t>enemy_animations_description</t>
   </si>
   <si>
     <t xml:space="preserve">Toggles enemy animations,\n can improve performance on low-end devices.</t>
@@ -204,7 +229,7 @@
     <t xml:space="preserve">Включает или отключает анимации противника, может увеличить\nпроизводительность на слабых устройствах.</t>
   </si>
   <si>
-    <t xml:space="preserve">ui_animations</t>
+    <t>ui_animations</t>
   </si>
   <si>
     <t xml:space="preserve">UI Animations</t>
@@ -213,7 +238,7 @@
     <t xml:space="preserve">Анимация пол. интерфейса</t>
   </si>
   <si>
-    <t xml:space="preserve">ui_animations_description</t>
+    <t>ui_animations_description</t>
   </si>
   <si>
     <t xml:space="preserve">Toggles ui animations,\n can improve performance on low-end devices.</t>
@@ -222,7 +247,7 @@
     <t xml:space="preserve">Включает или отключает анимации интерфейса, может увеличить\nпроизводительность на слабых устройствах.</t>
   </si>
   <si>
-    <t xml:space="preserve">blur_bg</t>
+    <t>blur_bg</t>
   </si>
   <si>
     <t xml:space="preserve">BG Blur</t>
@@ -231,7 +256,7 @@
     <t xml:space="preserve">Размития фона</t>
   </si>
   <si>
-    <t xml:space="preserve">blur_bg_description</t>
+    <t>blur_bg_description</t>
   </si>
   <si>
     <t xml:space="preserve">Toggles background blur on menus,\n can improve performance on low-end devices.</t>
@@ -240,7 +265,7 @@
     <t xml:space="preserve">Включает или отключает размития фона в меню, может увеличить\nпроизводительность на слабых устройствах.</t>
   </si>
   <si>
-    <t xml:space="preserve">sound_volume</t>
+    <t>sound_volume</t>
   </si>
   <si>
     <t xml:space="preserve">Sound Volume</t>
@@ -249,7 +274,7 @@
     <t xml:space="preserve">Громкость Звука</t>
   </si>
   <si>
-    <t xml:space="preserve">music_volume</t>
+    <t>music_volume</t>
   </si>
   <si>
     <t xml:space="preserve">Music Volune</t>
@@ -258,7 +283,7 @@
     <t xml:space="preserve">Громкость Музики</t>
   </si>
   <si>
-    <t xml:space="preserve">download_music_dlc_btn</t>
+    <t>download_music_dlc_btn</t>
   </si>
   <si>
     <t xml:space="preserve">Download Additional Music DLC</t>
@@ -267,7 +292,7 @@
     <t xml:space="preserve">Скачать доп. музыкальное DLC </t>
   </si>
   <si>
-    <t xml:space="preserve">redownload_music_dlc_btn</t>
+    <t>redownload_music_dlc_btn</t>
   </si>
   <si>
     <t xml:space="preserve">Redownload Additional Music DLC</t>
@@ -276,7 +301,7 @@
     <t xml:space="preserve">Перекачать доп. музыкальное DLC </t>
   </si>
   <si>
-    <t xml:space="preserve">remove_music_dlc_btn</t>
+    <t>remove_music_dlc_btn</t>
   </si>
   <si>
     <t xml:space="preserve">Remove Additional Music DLC</t>
@@ -285,7 +310,7 @@
     <t xml:space="preserve">Удалить доп. музыкальное DLC </t>
   </si>
   <si>
-    <t xml:space="preserve">download_music_dlc_description</t>
+    <t>download_music_dlc_description</t>
   </si>
   <si>
     <t xml:space="preserve">Downloads Additional Music DLC from Google Drive 
@@ -300,7 +325,7 @@
 Если загрузка с сервера будет слишком интенсивной, она может не работать. </t>
   </si>
   <si>
-    <t xml:space="preserve">remove_music_dlc_description</t>
+    <t>remove_music_dlc_description</t>
   </si>
   <si>
     <t xml:space="preserve">Deletes Additional Music DLC,\nbut you will lose additional music.</t>
@@ -309,16 +334,16 @@
     <t xml:space="preserve">Удаляет дополнительную музику DLC,\n но ты потеряешь дополнительную музыку. </t>
   </si>
   <si>
-    <t xml:space="preserve">language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Язик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skip_disclaimer</t>
+    <t>language</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Язик</t>
+  </si>
+  <si>
+    <t>skip_disclaimer</t>
   </si>
   <si>
     <t xml:space="preserve">Skip Disclaimer</t>
@@ -327,7 +352,7 @@
     <t xml:space="preserve">Пропустить дисклеймер</t>
   </si>
   <si>
-    <t xml:space="preserve">skip_disclaimer_description</t>
+    <t>skip_disclaimer_description</t>
   </si>
   <si>
     <t xml:space="preserve">If turned on Skips the disclaimer screen</t>
@@ -336,25 +361,25 @@
     <t xml:space="preserve">Если включено то екран дисклеймера будет пропущен</t>
   </si>
   <si>
-    <t xml:space="preserve">changelog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сhangelog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Изменения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Статистика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemies_killed</t>
+    <t>changelog</t>
+  </si>
+  <si>
+    <t>Сhangelog</t>
+  </si>
+  <si>
+    <t>Изменения</t>
+  </si>
+  <si>
+    <t>stats</t>
+  </si>
+  <si>
+    <t>Stats</t>
+  </si>
+  <si>
+    <t>Статистика</t>
+  </si>
+  <si>
+    <t>enemies_killed</t>
   </si>
   <si>
     <t xml:space="preserve">Enemies killed: </t>
@@ -363,7 +388,7 @@
     <t xml:space="preserve">Врагов убито: </t>
   </si>
   <si>
-    <t xml:space="preserve">droopers_bought</t>
+    <t>droopers_bought</t>
   </si>
   <si>
     <t xml:space="preserve">Droopers bought: </t>
@@ -372,7 +397,7 @@
     <t xml:space="preserve">Дроперов куплено:</t>
   </si>
   <si>
-    <t xml:space="preserve">upgrades_bought</t>
+    <t>upgrades_bought</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrades bought: </t>
@@ -381,7 +406,7 @@
     <t xml:space="preserve">Улучшенний куплено: </t>
   </si>
   <si>
-    <t xml:space="preserve">enemies_bought</t>
+    <t>enemies_bought</t>
   </si>
   <si>
     <t xml:space="preserve">Enemies bought: </t>
@@ -390,7 +415,7 @@
     <t xml:space="preserve">Врагов куплено: </t>
   </si>
   <si>
-    <t xml:space="preserve">coins_earned</t>
+    <t>coins_earned</t>
   </si>
   <si>
     <t xml:space="preserve">Coins earned: </t>
@@ -399,25 +424,25 @@
     <t xml:space="preserve">Монет накоплено: </t>
   </si>
   <si>
-    <t xml:space="preserve">time_played</t>
+    <t>time_played</t>
   </si>
   <si>
     <t xml:space="preserve">Time played: </t>
   </si>
   <si>
-    <t xml:space="preserve">Наиграно:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Благодарности</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credits_content</t>
+    <t>Наиграно:</t>
+  </si>
+  <si>
+    <t>credits</t>
+  </si>
+  <si>
+    <t>Credits</t>
+  </si>
+  <si>
+    <t>Благодарности</t>
+  </si>
+  <si>
+    <t>credits_content</t>
   </si>
   <si>
     <t xml:space="preserve">[color=#dbd9d9][wave amp=30.0 freq=4.0 connected=1]Original Creators[/wave][/color]
@@ -464,61 +489,61 @@
 Audacity</t>
   </si>
   <si>
-    <t xml:space="preserve">droopers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droopers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дроперы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Монеты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income</t>
+    <t>droopers</t>
+  </si>
+  <si>
+    <t>Droopers</t>
+  </si>
+  <si>
+    <t>Дроперы</t>
+  </si>
+  <si>
+    <t>coins</t>
+  </si>
+  <si>
+    <t>Coins</t>
+  </si>
+  <si>
+    <t>Монеты</t>
+  </si>
+  <si>
+    <t>income</t>
+  </si>
+  <si>
+    <t>Income</t>
   </si>
   <si>
     <t xml:space="preserve">Доход </t>
   </si>
   <si>
-    <t xml:space="preserve">enemies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enemies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Враги</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прокачка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">buy_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Купить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_btn</t>
+    <t>enemies</t>
+  </si>
+  <si>
+    <t>Enemies</t>
+  </si>
+  <si>
+    <t>Враги</t>
+  </si>
+  <si>
+    <t>upgrades</t>
+  </si>
+  <si>
+    <t>Upgrades</t>
+  </si>
+  <si>
+    <t>Прокачка</t>
+  </si>
+  <si>
+    <t>buy_btn</t>
+  </si>
+  <si>
+    <t>Buy</t>
+  </si>
+  <si>
+    <t>Купить</t>
+  </si>
+  <si>
+    <t>upgrade_btn</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrade Level </t>
@@ -527,16 +552,16 @@
     <t xml:space="preserve">Улучшить уровень </t>
   </si>
   <si>
-    <t xml:space="preserve">enemy_change_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сменить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price</t>
+    <t>enemy_change_btn</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Сменить</t>
+  </si>
+  <si>
+    <t>price</t>
   </si>
   <si>
     <t xml:space="preserve">Price: </t>
@@ -545,7 +570,7 @@
     <t xml:space="preserve">Цена: </t>
   </si>
   <si>
-    <t xml:space="preserve">drooper_cooldown_name</t>
+    <t>drooper_cooldown_name</t>
   </si>
   <si>
     <t xml:space="preserve">Faster droopers</t>
@@ -554,7 +579,7 @@
     <t xml:space="preserve">Ускоренния дроперов</t>
   </si>
   <si>
-    <t xml:space="preserve">enemy_multiplier_name</t>
+    <t>enemy_multiplier_name</t>
   </si>
   <si>
     <t xml:space="preserve">Enemy multiplier</t>
@@ -563,7 +588,7 @@
     <t xml:space="preserve">Множитель врагов</t>
   </si>
   <si>
-    <t xml:space="preserve">drooper_cooldown_desc</t>
+    <t>drooper_cooldown_desc</t>
   </si>
   <si>
     <t xml:space="preserve">Speeds up droopers by 0.1 second</t>
@@ -572,7 +597,7 @@
     <t xml:space="preserve">Ускоряет скорость дроперов на 0.1 секунд</t>
   </si>
   <si>
-    <t xml:space="preserve">enemy_multiplier_desc</t>
+    <t>enemy_multiplier_desc</t>
   </si>
   <si>
     <t xml:space="preserve">Multiplies amount of coins from enemy</t>
@@ -581,16 +606,16 @@
     <t xml:space="preserve">Враги дают монеты на раза больше</t>
   </si>
   <si>
-    <t xml:space="preserve">autoclicker_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autoclicker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автокликер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autoclicker_desc</t>
+    <t>autoclicker_name</t>
+  </si>
+  <si>
+    <t>Autoclicker</t>
+  </si>
+  <si>
+    <t>Автокликер</t>
+  </si>
+  <si>
+    <t>autoclicker_desc</t>
   </si>
   <si>
     <t xml:space="preserve">Autoclicks the enemy each 5 seconds</t>
@@ -599,16 +624,16 @@
     <t xml:space="preserve">Автоматически нажамает на врага каждие 5 секунд</t>
   </si>
   <si>
-    <t xml:space="preserve">autoclicker_amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шт:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy_multiplier_text</t>
+    <t>autoclicker_amount</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Шт:</t>
+  </si>
+  <si>
+    <t>enemy_multiplier_text</t>
   </si>
   <si>
     <t xml:space="preserve">x Mult</t>
@@ -617,16 +642,16 @@
     <t xml:space="preserve">x Множ</t>
   </si>
   <si>
-    <t xml:space="preserve">drooper_cooldown_text</t>
+    <t>drooper_cooldown_text</t>
   </si>
   <si>
     <t xml:space="preserve">Cooldown: </t>
   </si>
   <si>
-    <t xml:space="preserve">Задержка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per_second</t>
+    <t>Задержка</t>
+  </si>
+  <si>
+    <t>per_second</t>
   </si>
   <si>
     <t xml:space="preserve">per second</t>
@@ -635,7 +660,7 @@
     <t xml:space="preserve">за секунду</t>
   </si>
   <si>
-    <t xml:space="preserve">per_click</t>
+    <t>per_click</t>
   </si>
   <si>
     <t xml:space="preserve">per kill</t>
@@ -644,7 +669,7 @@
     <t xml:space="preserve">за убивание</t>
   </si>
   <si>
-    <t xml:space="preserve">disclaimer_content</t>
+    <t>disclaimer_content</t>
   </si>
   <si>
     <t xml:space="preserve">This fan project is not endorsored
@@ -665,16 +690,16 @@
 @Maritosu на YouTube </t>
   </si>
   <si>
-    <t xml:space="preserve">disclaimer_btn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Внимание!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disclaimer_indev</t>
+    <t>disclaimer_btn</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>Внимание!</t>
+  </si>
+  <si>
+    <t>disclaimer_indev</t>
   </si>
   <si>
     <t xml:space="preserve">This game is still in development expect short playtime and less content.</t>
@@ -683,7 +708,7 @@
     <t xml:space="preserve">Эта игра еще в разработке и поэтому игровое\nвремя и контента может быть мало.</t>
   </si>
   <si>
-    <t xml:space="preserve">disclaimer_dev_version</t>
+    <t>disclaimer_dev_version</t>
   </si>
   <si>
     <t xml:space="preserve">You might be either playing or testing an version from the project’s source code, be warned that this version is unstable and most content is not finished you are warned.</t>
@@ -692,7 +717,7 @@
     <t xml:space="preserve">Ви играете или тестируете версию з исходного кода, ви можете увидеть баги и не завершенний контент ви били предупреждены.</t>
   </si>
   <si>
-    <t xml:space="preserve">not_enough_coins</t>
+    <t>not_enough_coins</t>
   </si>
   <si>
     <t xml:space="preserve">You don’t have enough coins to buy this item!</t>
@@ -701,7 +726,7 @@
     <t xml:space="preserve">У тебя недостаточно монет чтобы купить это!</t>
   </si>
   <si>
-    <t xml:space="preserve">upgrade_maxxed</t>
+    <t>upgrade_maxxed</t>
   </si>
   <si>
     <t xml:space="preserve">You have reached maximum level for this upgrade!</t>
@@ -713,42 +738,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <name val="Liberation Mono;Courier New"/>
-      <family val="3"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -760,74 +758,355 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Unknown Author" id="{66CEB279-F7E0-8681-85E4-B2167481CD40}"/>
+</personList>
+</file>
+
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -869,17 +1148,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -929,34 +1208,52 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D3" personId="{66CEB279-F7E0-8681-85E4-B2167481CD40}" id="{3E6082AE-427E-4561-BB04-4FFC2BCC68EC}" done="0">
+    <text xml:space="preserve">Settings menu
+</text>
+  </threadedComment>
+  <threadedComment ref="D30" personId="{66CEB279-F7E0-8681-85E4-B2167481CD40}" id="{9299A9CA-65C3-488D-A61A-5D15F38B91BC}" done="0">
+    <text xml:space="preserve">Store content
+</text>
+  </threadedComment>
+  <threadedComment ref="D50" personId="{66CEB279-F7E0-8681-85E4-B2167481CD40}" id="{3A800AE9-6966-4314-9858-99499E309450}" done="0">
+    <text xml:space="preserve">Disclaimer content
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62.13"/>
+    <col customWidth="1" min="1" max="1" style="1" width="29.530000000000001"/>
+    <col customWidth="1" min="2" max="2" style="1" width="51.719999999999999"/>
+    <col customWidth="1" min="3" max="3" style="1" width="62.130000000000003"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.800000000000001">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12.800000000000001">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -967,7 +1264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="12.800000000000001">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -978,7 +1275,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="12.800000000000001">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -989,7 +1286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.800000000000001">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1000,7 +1297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.800000000000001">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1011,7 +1308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.800000000000001">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1022,7 +1319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.800000000000001">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1033,7 +1330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.800000000000001">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -1044,7 +1341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.800000000000001">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1055,7 +1352,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.800000000000001">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1066,7 +1363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.800000000000001">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -1077,7 +1374,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.800000000000001">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1088,7 +1385,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.800000000000001">
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
@@ -1099,7 +1396,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.800000000000001">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -1110,7 +1407,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.800000000000001">
       <c r="A16" s="1" t="s">
         <v>45</v>
       </c>
@@ -1121,7 +1418,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.800000000000001">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -1132,7 +1429,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.800000000000001">
       <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
@@ -1143,7 +1440,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.800000000000001">
       <c r="A19" s="1" t="s">
         <v>54</v>
       </c>
@@ -1154,7 +1451,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.800000000000001">
       <c r="A20" s="1" t="s">
         <v>57</v>
       </c>
@@ -1165,7 +1462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.800000000000001">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
@@ -1176,62 +1473,62 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="13.5">
       <c r="A22" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="13.5">
       <c r="A23" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="13.5">
       <c r="A24" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="81">
       <c r="A25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="13.5">
       <c r="A26" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.800000000000001">
       <c r="A27" s="1" t="s">
         <v>78</v>
       </c>
@@ -1242,7 +1539,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.800000000000001">
       <c r="A28" s="1" t="s">
         <v>81</v>
       </c>
@@ -1253,7 +1550,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.800000000000001">
       <c r="A29" s="1" t="s">
         <v>84</v>
       </c>
@@ -1264,7 +1561,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.800000000000001">
       <c r="A30" s="1" t="s">
         <v>87</v>
       </c>
@@ -1275,84 +1572,84 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="31" ht="12.800000000000001">
+      <c r="A31" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="32" ht="12.800000000000001">
+      <c r="A32" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" ht="12.800000000000001">
+      <c r="A33" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="34" ht="12.800000000000001">
+      <c r="A34" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="35" ht="12.800000000000001">
+      <c r="A35" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+    <row r="36" ht="12.800000000000001">
+      <c r="A36" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="37" ht="12.800000000000001">
+      <c r="A37" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.800000000000001">
       <c r="A38" s="1" t="s">
         <v>111</v>
       </c>
@@ -1363,18 +1660,18 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="398" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="409.5">
       <c r="A39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.800000000000001">
       <c r="A40" s="1" t="s">
         <v>117</v>
       </c>
@@ -1385,7 +1682,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.800000000000001">
       <c r="A41" s="1" t="s">
         <v>120</v>
       </c>
@@ -1396,18 +1693,18 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="12.800000000000001">
       <c r="A42" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.800000000000001">
       <c r="A43" s="1" t="s">
         <v>126</v>
       </c>
@@ -1418,7 +1715,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.800000000000001">
       <c r="A44" s="1" t="s">
         <v>129</v>
       </c>
@@ -1429,7 +1726,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.800000000000001">
       <c r="A45" s="1" t="s">
         <v>132</v>
       </c>
@@ -1440,7 +1737,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.800000000000001">
       <c r="A46" s="1" t="s">
         <v>135</v>
       </c>
@@ -1451,7 +1748,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.800000000000001">
       <c r="A47" s="1" t="s">
         <v>138</v>
       </c>
@@ -1462,7 +1759,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.800000000000001">
       <c r="A48" s="1" t="s">
         <v>141</v>
       </c>
@@ -1473,7 +1770,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.800000000000001">
       <c r="A49" s="1" t="s">
         <v>144</v>
       </c>
@@ -1484,7 +1781,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.800000000000001">
       <c r="A50" s="1" t="s">
         <v>147</v>
       </c>
@@ -1495,7 +1792,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.800000000000001">
       <c r="A51" s="1" t="s">
         <v>150</v>
       </c>
@@ -1506,7 +1803,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.800000000000001">
       <c r="A52" s="1" t="s">
         <v>153</v>
       </c>
@@ -1517,7 +1814,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.800000000000001">
       <c r="A53" s="1" t="s">
         <v>156</v>
       </c>
@@ -1528,7 +1825,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.800000000000001">
       <c r="A54" s="1" t="s">
         <v>159</v>
       </c>
@@ -1539,7 +1836,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="12.800000000000001">
       <c r="A55" s="1" t="s">
         <v>162</v>
       </c>
@@ -1550,7 +1847,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="12.800000000000001">
       <c r="A56" s="1" t="s">
         <v>165</v>
       </c>
@@ -1561,7 +1858,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="12.800000000000001">
       <c r="A57" s="1" t="s">
         <v>168</v>
       </c>
@@ -1572,7 +1869,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.800000000000001">
       <c r="A58" s="1" t="s">
         <v>171</v>
       </c>
@@ -1583,7 +1880,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.800000000000001">
       <c r="A59" s="1" t="s">
         <v>174</v>
       </c>
@@ -1594,18 +1891,18 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="103.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="121.5">
       <c r="A60" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="12.800000000000001">
       <c r="A61" s="1" t="s">
         <v>180</v>
       </c>
@@ -1616,7 +1913,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="12.800000000000001">
       <c r="A62" s="1" t="s">
         <v>183</v>
       </c>
@@ -1627,7 +1924,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.800000000000001">
       <c r="A63" s="1" t="s">
         <v>186</v>
       </c>
@@ -1638,7 +1935,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.800000000000001">
       <c r="A64" s="1" t="s">
         <v>189</v>
       </c>
@@ -1649,7 +1946,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" ht="12.800000000000001">
       <c r="A65" s="1" t="s">
         <v>192</v>
       </c>
@@ -1660,24 +1957,24 @@
         <v>194</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0"/>
-      <c r="B66" s="0"/>
-      <c r="C66" s="0"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0"/>
-      <c r="B67" s="0"/>
-      <c r="C67" s="0"/>
+    <row r="66" ht="12.800000000000001">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+    </row>
+    <row r="67" ht="12.800000000000001">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.05277777777778" bottom="1.05277777777778" header="0.78750000000000009" footer="0.78750000000000009"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>